--- a/data/卡牌圖鑑_v1.0.2.xlsx
+++ b/data/卡牌圖鑑_v1.0.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D08351-DE24-4F23-9A4D-C88AAFA5C110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD5DF22-F029-4AD4-A76C-A0DD8931949C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22920" yWindow="3720" windowWidth="21255" windowHeight="11565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="主角圖鑑" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="設計說明與統計" sheetId="2" r:id="rId3"/>
     <sheet name="費用與效果統計" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'卡牌圖鑑_v1.0.2'!$A$1:$H$55</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -3066,6 +3069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3102,7 +3106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="45" customHeight="1">
+    <row r="2" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>202</v>
       </c>
@@ -3126,7 +3130,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="45" customHeight="1">
+    <row r="3" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1">
+    <row r="4" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>15</v>
       </c>
@@ -3174,7 +3178,7 @@
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1">
+    <row r="5" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -3191,14 +3195,14 @@
         <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="9"/>
     </row>
-    <row r="6" spans="1:8" ht="45" customHeight="1">
+    <row r="6" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
@@ -3222,7 +3226,7 @@
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1">
+    <row r="7" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -3246,7 +3250,7 @@
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" ht="45" customHeight="1">
+    <row r="8" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
@@ -3270,7 +3274,7 @@
       </c>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="1:8" ht="45" customHeight="1">
+    <row r="9" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
@@ -3390,7 +3394,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -3435,14 +3439,14 @@
         <v>30</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" ht="45" customHeight="1">
+    <row r="16" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>46</v>
       </c>
@@ -3466,7 +3470,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="45" customHeight="1">
+    <row r="17" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>52</v>
       </c>
@@ -3492,7 +3496,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="45" customHeight="1">
+    <row r="18" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>54</v>
       </c>
@@ -3518,7 +3522,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="45" customHeight="1">
+    <row r="19" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>57</v>
       </c>
@@ -3544,7 +3548,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="45" customHeight="1">
+    <row r="20" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -3568,7 +3572,7 @@
       </c>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" ht="45" customHeight="1">
+    <row r="21" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>62</v>
       </c>
@@ -3592,7 +3596,7 @@
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" ht="45" customHeight="1">
+    <row r="22" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>78</v>
       </c>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" ht="45" customHeight="1">
+    <row r="23" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>95</v>
       </c>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1">
+    <row r="24" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>64</v>
       </c>
@@ -3664,7 +3668,7 @@
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" ht="45" customHeight="1">
+    <row r="25" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>67</v>
       </c>
@@ -3688,7 +3692,7 @@
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" ht="45" customHeight="1">
+    <row r="26" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>69</v>
       </c>
@@ -3712,7 +3716,7 @@
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" ht="45" customHeight="1">
+    <row r="27" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>71</v>
       </c>
@@ -3888,7 +3892,7 @@
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="45" customHeight="1">
+    <row r="34" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>93</v>
       </c>
@@ -3914,7 +3918,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="45" customHeight="1">
+    <row r="35" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>99</v>
       </c>
@@ -3940,7 +3944,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="45" customHeight="1">
+    <row r="36" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>102</v>
       </c>
@@ -3966,7 +3970,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="45" customHeight="1">
+    <row r="37" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>106</v>
       </c>
@@ -3992,7 +3996,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="45" customHeight="1">
+    <row r="38" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>108</v>
       </c>
@@ -4018,7 +4022,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="45" customHeight="1">
+    <row r="39" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>111</v>
       </c>
@@ -4042,7 +4046,7 @@
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="45" customHeight="1">
+    <row r="40" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>113</v>
       </c>
@@ -4066,7 +4070,7 @@
       </c>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" ht="45" customHeight="1">
+    <row r="41" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>127</v>
       </c>
@@ -4090,7 +4094,7 @@
       </c>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" ht="45" customHeight="1">
+    <row r="42" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>140</v>
       </c>
@@ -4114,7 +4118,7 @@
       </c>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" ht="45" customHeight="1">
+    <row r="43" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>115</v>
       </c>
@@ -4138,7 +4142,7 @@
       </c>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" ht="45" customHeight="1">
+    <row r="44" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>117</v>
       </c>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" ht="45" customHeight="1">
+    <row r="45" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>119</v>
       </c>
@@ -4203,7 +4207,7 @@
         <v>30</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>129</v>
@@ -4253,12 +4257,12 @@
         <v>17</v>
       </c>
       <c r="F48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H48" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="45" customHeight="1">
       <c r="A49" s="2" t="s">
@@ -4303,7 +4307,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>11</v>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" ht="45" customHeight="1">
+    <row r="52" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
@@ -4360,7 +4364,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="45" customHeight="1">
+    <row r="53" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>143</v>
       </c>
@@ -4386,7 +4390,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="45" customHeight="1">
+    <row r="54" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>145</v>
       </c>
@@ -4412,7 +4416,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="45" customHeight="1">
+    <row r="55" spans="1:8" ht="45" hidden="1" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>147</v>
       </c>
@@ -4439,6 +4443,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H55" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
